--- a/data/trans_orig/IQ22A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias</t>
+          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias (tasa de respuesta: 93,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,59</t>
+          <t>1,57; 2,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,16</t>
+          <t>1,81; 3,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,73</t>
+          <t>1,66; 2,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,3</t>
+          <t>1,62; 3,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,67</t>
+          <t>1,7; 2,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,07</t>
+          <t>1,84; 2,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,08</t>
+          <t>1,84; 2,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,44</t>
+          <t>1,58; 3,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,36</t>
+          <t>1,73; 2,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 2,84</t>
+          <t>1,95; 2,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,6</t>
+          <t>1,85; 2,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,92</t>
+          <t>1,75; 2,92</t>
         </is>
       </c>
     </row>
@@ -856,47 +856,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,99</t>
+          <t>1,34; 1,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,38</t>
+          <t>1,64; 2,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,34</t>
+          <t>1,72; 3,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,9</t>
+          <t>1,97; 3,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,82</t>
+          <t>1,45; 1,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,0</t>
+          <t>1,52; 2,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,36</t>
+          <t>1,54; 2,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,01</t>
+          <t>1,68; 2,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,77</t>
+          <t>1,44; 1,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,6</t>
+          <t>1,73; 2,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,08</t>
+          <t>1,93; 3,04</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,13</t>
+          <t>1,15; 2,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,92</t>
+          <t>1,24; 1,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,23</t>
+          <t>1,48; 2,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,65</t>
+          <t>1,09; 2,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,85</t>
+          <t>1,17; 1,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,56</t>
+          <t>1,15; 1,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,8</t>
+          <t>1,37; 2,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,76</t>
+          <t>1,15; 1,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,85</t>
+          <t>1,21; 1,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,62</t>
+          <t>1,24; 1,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,24</t>
+          <t>1,52; 2,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,98</t>
+          <t>1,22; 1,96</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,76</t>
+          <t>1,14; 1,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,55</t>
+          <t>1,28; 2,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,47 +1151,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,74</t>
+          <t>1,18; 1,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,9</t>
+          <t>1,23; 1,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,44</t>
+          <t>1,13; 1,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,8</t>
+          <t>1,19; 1,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,75</t>
+          <t>1,44; 2,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,68</t>
+          <t>1,23; 1,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,68</t>
+          <t>1,22; 1,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,64</t>
+          <t>1,21; 1,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,04</t>
+          <t>1,38; 2,01</t>
         </is>
       </c>
     </row>
@@ -1276,22 +1276,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,79</t>
+          <t>1,41; 1,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,28</t>
+          <t>1,73; 2,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,32</t>
+          <t>1,69; 2,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,19</t>
+          <t>1,56; 2,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,85</t>
+          <t>1,52; 1,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,11</t>
+          <t>1,62; 2,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,95</t>
+          <t>1,67; 1,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,13</t>
+          <t>1,72; 2,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,09</t>
+          <t>1,66; 2,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Edad-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,59</t>
+          <t>1,58; 2,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,03</t>
+          <t>1,83; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,68</t>
+          <t>1,66; 2,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,25</t>
+          <t>1,64; 3,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,54</t>
+          <t>1,73; 2,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,99</t>
+          <t>1,84; 3,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,98</t>
+          <t>1,85; 3,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,51</t>
+          <t>1,59; 3,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,37</t>
+          <t>1,75; 2,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,81</t>
+          <t>1,96; 2,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,59</t>
+          <t>1,84; 2,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,92</t>
+          <t>1,76; 3,01</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,97</t>
+          <t>1,33; 1,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,37</t>
+          <t>1,64; 2,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,58</t>
+          <t>1,72; 3,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,76</t>
+          <t>1,97; 3,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 1,8</t>
+          <t>1,44; 1,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,03</t>
+          <t>1,52; 2,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,34</t>
+          <t>1,55; 2,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,99</t>
+          <t>1,68; 2,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,75</t>
+          <t>1,45; 1,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,06</t>
+          <t>1,62; 2,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,69</t>
+          <t>1,75; 2,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,04</t>
+          <t>1,93; 2,98</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,17</t>
+          <t>1,15; 2,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,91</t>
+          <t>1,27; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,22</t>
+          <t>1,51; 2,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,76</t>
+          <t>1,07; 2,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,84</t>
+          <t>1,17; 1,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,58</t>
+          <t>1,14; 1,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,77</t>
+          <t>1,37; 2,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,77</t>
+          <t>1,15; 1,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,79</t>
+          <t>1,22; 1,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,63</t>
+          <t>1,24; 1,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,29</t>
+          <t>1,52; 2,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,96</t>
+          <t>1,2; 1,95</t>
         </is>
       </c>
     </row>
@@ -1136,52 +1136,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,74</t>
+          <t>1,12; 1,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,58</t>
+          <t>1,27; 2,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,64</t>
+          <t>1,1; 1,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,68</t>
+          <t>1,17; 1,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,89</t>
+          <t>1,22; 1,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,43</t>
+          <t>1,13; 1,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,81</t>
+          <t>1,19; 1,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,66</t>
+          <t>1,46; 2,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,67</t>
+          <t>1,23; 1,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,61</t>
+          <t>1,23; 1,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,01</t>
+          <t>1,41; 2,04</t>
         </is>
       </c>
     </row>
@@ -1276,37 +1276,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,78</t>
+          <t>1,42; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,29</t>
+          <t>1,73; 2,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,34</t>
+          <t>1,68; 2,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,2</t>
+          <t>1,61; 2,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,82</t>
+          <t>1,51; 1,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,86</t>
+          <t>1,53; 1,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,13</t>
+          <t>1,61; 2,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,75</t>
+          <t>1,51; 1,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,97</t>
+          <t>1,67; 1,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,12</t>
+          <t>1,74; 2,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,07</t>
+          <t>1,67; 2,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,89</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,03</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,22</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,55</t>
+          <t>1,71; 2,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,05</t>
+          <t>1,87; 3,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,84</t>
+          <t>1,84; 3,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,18</t>
+          <t>1,56; 3,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,64</t>
+          <t>1,59; 2,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,01</t>
+          <t>1,8; 3,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,04</t>
+          <t>1,66; 2,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,45</t>
+          <t>1,66; 3,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,4</t>
+          <t>1,7; 2,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 2,82</t>
+          <t>1,96; 2,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,57</t>
+          <t>1,84; 2,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,01</t>
+          <t>1,75; 2,9</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,71</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,24</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,52</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,91</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,19</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,47</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,98</t>
+          <t>1,44; 1,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1,53; 2,0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1,57; 2,36</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1,72; 2,96</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,33; 1,99</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1,64; 2,38</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 3,29</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,97; 3,92</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 1,81</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 2,01</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,39</t>
+          <t>1,68; 3,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,98</t>
+          <t>1,96; 4,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 1,78</t>
+          <t>1,44; 1,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,03</t>
+          <t>1,63; 2,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,76</t>
+          <t>1,73; 2,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,98</t>
+          <t>2,04; 3,14</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,78</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,51</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>1,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,47 +996,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,3</t>
+          <t>1,16; 1,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,98</t>
+          <t>1,14; 1,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,26</t>
+          <t>1,36; 2,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,57</t>
+          <t>1,15; 1,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,83</t>
+          <t>1,15; 2,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,56</t>
+          <t>1,25; 1,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,66</t>
+          <t>1,49; 2,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,76</t>
+          <t>1,11; 2,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,79</t>
+          <t>1,24; 1,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,27</t>
+          <t>1,51; 2,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,95</t>
+          <t>1,21; 1,99</t>
         </is>
       </c>
     </row>
@@ -1068,62 +1068,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,44</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,64</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,31</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,29</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1,39</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>1,39</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,58</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1,22; 1,9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1,13; 1,44</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1,2; 1,8</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1,47; 2,67</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1,12; 1,76</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 2,86</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 1,68</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 1,65</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 1,91</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,41</t>
+          <t>1,25; 2,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,84</t>
+          <t>1,12; 1,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,66</t>
+          <t>1,14; 1,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,66</t>
+          <t>1,23; 1,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,65</t>
+          <t>1,23; 1,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,66</t>
+          <t>1,22; 1,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,04</t>
+          <t>1,35; 1,96</t>
         </is>
       </c>
     </row>
@@ -1208,62 +1208,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,95</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,92</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,82</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,8</t>
+          <t>1,52; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,27</t>
+          <t>1,53; 1,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,33</t>
+          <t>1,63; 2,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,2</t>
+          <t>1,59; 2,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,81</t>
+          <t>1,4; 1,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,87</t>
+          <t>1,72; 2,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,13</t>
+          <t>1,71; 2,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,21</t>
+          <t>1,54; 2,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,74</t>
+          <t>1,51; 1,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,13</t>
+          <t>1,72; 2,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,09</t>
+          <t>1,63; 2,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias (tasa de respuesta: 93,84%)</t>
+          <t>Número medio de veces que los menores utilizaron algún servicio de urgencias en los últimos 12 meses (tasa de respuesta: 93,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.081374434464071</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.301569039680298</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.304179567653811</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.291118299503439</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.890607769340516</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.320587199522872</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.028809965570209</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2.161083727190284</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1.986274765932729</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2.312415572833934</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2.15645047663323</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>2.218264426618232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 2,67</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 3,07</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,84; 3,08</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 3,46</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 2,59</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 3,16</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 2,73</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 3,24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1,7; 2,36</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,96; 2,84</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,84; 2,6</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,75; 2,9</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.712996267146241</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.867564757149468</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.84283179702541</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.564585559285692</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.592804213159458</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.804825575381624</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.660037570217819</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.656458911743743</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.695590927536348</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1.955053140735484</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.835669815162325</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>1.750576618476505</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.665402727225008</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.06725702684321</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.075677105366355</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.459004457025971</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.587891206586459</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3.157335340556404</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2.727209818229969</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3.244728422608593</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2.357662473789753</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>2.841454062617662</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>2.602346316430759</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>2.904328624243661</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 1,82</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 2,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,57; 2,36</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 2,96</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,33; 1,99</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,64; 2,38</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 3,34</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,96; 4,13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 1,77</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 2,06</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,73; 2,6</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,04; 3,14</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.612086601805503</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.714636267132364</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.842470657890433</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2.240827189819551</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1.519805729266362</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.914359141930983</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2.193397692582809</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>2.741236317809427</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.572479548841469</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.803641068708497</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>2.02588372801655</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>2.466244960226021</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.441893379182854</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.527060229428876</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.573867223110605</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1.723818485965277</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.326432551372557</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.637206984843609</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.680623099621683</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.963097784686137</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1.439714445912886</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.634705467780558</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.725828477644321</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>2.038550596529913</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 1,85</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 1,56</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,36; 2,8</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 1,74</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 2,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 1,92</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 2,23</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 2,67</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 1,85</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 1,62</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 2,24</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,99</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.824153193643207</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.995859707973279</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.362671769214808</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.958204843299289</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1.985129686089146</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2.384147165858622</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>3.343455327020735</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>4.131449984221238</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1.774256899092861</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2.062298896891388</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2.59892770248939</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>3.138851561403173</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,58</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.404292203707198</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.298288716057245</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.776977926531476</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.351718707040979</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.428827769735333</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.505354940298585</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.803357067898658</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.569793648704047</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.417051204423135</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1.391521879925562</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.790287067986943</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.44860862320616</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 1,9</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,13; 1,44</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 1,8</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 2,67</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 1,76</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 2,55</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 1,64</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 1,59</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,68</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,68</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 1,64</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 1,96</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.163192173232178</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.135053746830122</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.36384919484235</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.149189145557873</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.145315916257593</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.251990568267572</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.494684290233193</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1.110994683730789</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.241850248591355</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.24075180429955</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.513866874233577</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1.206917182122828</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.846997971319404</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.558091653949011</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.798890101994223</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.740104285305456</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.134622983076007</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1.916160232069321</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>2.230812820517664</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2.673851452771513</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1.852046607485022</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1.624985475697773</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>2.240778627106989</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>1.992813046973445</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.454543654139776</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.247771368643583</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.438845253717627</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.869681800216701</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.315011109813232</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1.640732910262078</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.308803481744718</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1.290776967087113</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1.39349081922057</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1.364309068980584</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1.38949890221014</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1.582460726715277</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.223113356805001</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.134583659238063</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.203146458211695</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.470837054729647</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.123843687297982</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1.254218603916819</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.117456607241224</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1.139573242261339</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.234698106717071</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.233597665337637</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.217678507397063</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1.345859727750528</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.899229933835062</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.436423051281576</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.798897367421773</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.666168659179291</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1.762447395028601</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2.547193901964779</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1.638507045641659</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>1.59103764535623</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1.676851236419</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>1.679462158272024</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1.636224308062964</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1.958345258259221</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 1,82</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 1,85</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 2,11</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 2,17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 1,79</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 2,28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 2,32</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 2,18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 1,75</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1,67; 1,95</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 2,13</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 2,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.653874766310953</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.667052055658169</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.829099808388757</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.839057176208506</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.559246047567587</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.95066693665458</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.923842161123752</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1.790663312396934</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.610314081910222</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.794890953538632</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1.875920111518822</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1.815892751960453</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.517190796475913</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.533957283200616</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.625350328521838</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1.594982691911127</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.404572583611406</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1.715364814633934</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1.707208800738527</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1.541333776280006</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>1.506165429943796</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1.670005802589399</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1.720522120322726</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1.625549578112234</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.822096524924422</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.850526452158602</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.11485078907165</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.170824829565978</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.792786820444103</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.283285123652623</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.322561412158959</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>2.175962439952529</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1.747753874559038</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1.949470704506522</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>2.127419887331808</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>2.052742234079716</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
